--- a/examples/Диплом_1_ведомость_формовки.xlsx
+++ b/examples/Диплом_1_ведомость_формовки.xlsx
@@ -68,6 +68,9 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
 </styleSheet>
 </file>
 
